--- a/data/trending_integrated_20260922_09.xlsx
+++ b/data/trending_integrated_20260922_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>327000</v>
+        <v>65000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+2.67%</t>
+          <t>'+24.28%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.4</v>
+        <v>-0.01</v>
       </c>
       <c r="E2" t="n">
         <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="H2" t="n">
-        <v>3.22</v>
+        <v>6.87</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>318500</v>
+        <v>52300</v>
       </c>
       <c r="K2" t="n">
-        <v>333000</v>
+        <v>60800</v>
       </c>
       <c r="L2" t="n">
-        <v>333000</v>
+        <v>65700</v>
       </c>
       <c r="M2" t="n">
-        <v>326500</v>
+        <v>59700</v>
       </c>
       <c r="N2" t="n">
-        <v>3.62</v>
+        <v>6.88</v>
       </c>
       <c r="O2" t="n">
-        <v>4829634500</v>
+        <v>30560415350</v>
       </c>
       <c r="P2" t="n">
-        <v>635000</v>
+        <v>148300</v>
       </c>
       <c r="Q2" t="n">
-        <v>52600</v>
+        <v>16300</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,20 +626,20 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>나스닥 및 미국 증시 상승, 구리 가격 상승, AI 관련주 강세에 따른 가온전선 주가 상승 기대감. 40만원 돌파 및 52주 신고가 도전 언급.</t>
+          <t>GDDR7 기판 공급망 합류 뉴스 기반 급등. 개인 투자자 매도 압력 존재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['나스닥', '구리가격', 'AI관련주']</t>
+          <t>['GDDR7', '기판', '공급망']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1916000</v>
+        <v>332500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+2.57%</t>
+          <t>'+4.40%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.06</v>
+        <v>-0.4</v>
       </c>
       <c r="E3" t="n">
-        <v>450</v>
+        <v>47</v>
       </c>
       <c r="F3" t="n">
-        <v>295</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>2553</v>
+        <v>140</v>
       </c>
       <c r="H3" t="n">
-        <v>50.17</v>
+        <v>3.22</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1868000</v>
+        <v>318500</v>
       </c>
       <c r="K3" t="n">
-        <v>1909000</v>
+        <v>333000</v>
       </c>
       <c r="L3" t="n">
-        <v>1922000</v>
+        <v>342000</v>
       </c>
       <c r="M3" t="n">
-        <v>1904000</v>
+        <v>325000</v>
       </c>
       <c r="N3" t="n">
-        <v>50.23</v>
+        <v>3.62</v>
       </c>
       <c r="O3" t="n">
-        <v>243535705500</v>
+        <v>29887121750</v>
       </c>
       <c r="P3" t="n">
-        <v>2987000</v>
+        <v>635000</v>
       </c>
       <c r="Q3" t="n">
-        <v>333000</v>
+        <v>52600</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,29 +718,397 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 증시 및 반도체주 강세에 따른 SK하이닉스 주가 상승 기대감. 200만 돌파 및 500만원 목표 제시.</t>
+          <t>신고가 랠리 기대감 및 전력주 강세. AI 관련주 및 국제유가 하락 수혜.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>['신고가', '전력주', 'AI']</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>000500</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1934000</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>'+3.53%</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="E4" t="n">
+        <v>509</v>
+      </c>
+      <c r="F4" t="n">
+        <v>333</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2749</v>
+      </c>
+      <c r="H4" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1868000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1909000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1935000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1904000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>50.23</v>
+      </c>
+      <c r="O4" t="n">
+        <v>693901669000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>333000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>미국 증시 및 반도체주 강세에 따른 SK하이닉스 주가 상승 기대감. 200만 돌파 및 500만원 목표 제시.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
         <v>0.3</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>['미국증시', '반도체주', '목표가']</t>
         </is>
       </c>
-      <c r="X3" t="n">
+      <c r="X4" t="n">
         <v>76</v>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>281500</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'+2.74%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>673</v>
+      </c>
+      <c r="F5" t="n">
+        <v>427</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3981</v>
+      </c>
+      <c r="H5" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>274000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>283000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>283500</v>
+      </c>
+      <c r="M5" t="n">
+        <v>280000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="O5" t="n">
+        <v>445118650250</v>
+      </c>
+      <c r="P5" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>81100</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>3분기 영업이익 호조 및 30만 전자 돌파 기대감. 미 증시 반도체주 급등.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['영업이익', '반도체', '미증시']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>111</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>17890</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'+0.96%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="E6" t="n">
+        <v>74</v>
+      </c>
+      <c r="F6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" t="n">
+        <v>309</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>17720</v>
+      </c>
+      <c r="K6" t="n">
+        <v>18230</v>
+      </c>
+      <c r="L6" t="n">
+        <v>18750</v>
+      </c>
+      <c r="M6" t="n">
+        <v>17500</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>55524429405</v>
+      </c>
+      <c r="P6" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1272</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>AI 데이터 관련 낙관론 및 미국 광통신주 급등 수혜 기대. 코스닥 대장주 급등 출발.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['AI', '광통신', '코스닥']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>85800</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'+0.59%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>99</v>
+      </c>
+      <c r="F7" t="n">
+        <v>68</v>
+      </c>
+      <c r="G7" t="n">
+        <v>463</v>
+      </c>
+      <c r="H7" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>85300</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>87000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>85500</v>
+      </c>
+      <c r="N7" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="O7" t="n">
+        <v>30178877800</v>
+      </c>
+      <c r="P7" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>미국 SMR 사업 추진 확정 및 공급 계약 체결. 차세대 KDDX 전기추진 시스템 공급 계약.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['SMR', '공급 계약', 'KDDX']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>034020</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260922_09.xlsx
+++ b/data/trending_integrated_20260922_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>65000</v>
+        <v>63600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+24.28%</t>
+          <t>'+21.61%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H2" t="n">
         <v>6.87</v>
@@ -610,7 +610,7 @@
         <v>6.88</v>
       </c>
       <c r="O2" t="n">
-        <v>30560415350</v>
+        <v>43627337200</v>
       </c>
       <c r="P2" t="n">
         <v>148300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>GDDR7 기판 공급망 합류 뉴스 기반 급등. 개인 투자자 매도 압력 존재.</t>
+          <t>SK하이닉스의 GDDR7 기판 공급망 합류 관련 뉴스 기반 주가 상승 기대. 일부 매도 의견 혼재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['GDDR7', '기판', '공급망']</t>
+          <t>['GDDR7', '반도체', '기판']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,60 +655,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>332500</v>
+        <v>6340</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+4.40%</t>
+          <t>'+8.19%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.4</v>
+        <v>-0.19</v>
       </c>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
         <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="H3" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>318500</v>
+        <v>5860</v>
       </c>
       <c r="K3" t="n">
-        <v>333000</v>
+        <v>6200</v>
       </c>
       <c r="L3" t="n">
-        <v>342000</v>
+        <v>6610</v>
       </c>
       <c r="M3" t="n">
-        <v>325000</v>
+        <v>6150</v>
       </c>
       <c r="N3" t="n">
-        <v>3.62</v>
+        <v>0.19</v>
       </c>
       <c r="O3" t="n">
-        <v>29887121750</v>
+        <v>28193598825</v>
       </c>
       <c r="P3" t="n">
-        <v>635000</v>
+        <v>13140</v>
       </c>
       <c r="Q3" t="n">
-        <v>52600</v>
+        <v>3725</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>신고가 랠리 기대감 및 전력주 강세. AI 관련주 및 국제유가 하락 수혜.</t>
+          <t>비트코인 급등 및 가상화폐 테마 강세에 따른 주가 상승 전망. 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['신고가', '전력주', 'AI']</t>
+          <t>['비트코인', '가상화폐', '공매도']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1934000</v>
+        <v>332500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+3.53%</t>
+          <t>'+4.40%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.06</v>
+        <v>-0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>509</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
-        <v>333</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>2749</v>
+        <v>140</v>
       </c>
       <c r="H4" t="n">
-        <v>50.17</v>
+        <v>3.22</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1868000</v>
+        <v>318500</v>
       </c>
       <c r="K4" t="n">
-        <v>1909000</v>
+        <v>333000</v>
       </c>
       <c r="L4" t="n">
-        <v>1935000</v>
+        <v>342000</v>
       </c>
       <c r="M4" t="n">
-        <v>1904000</v>
+        <v>325000</v>
       </c>
       <c r="N4" t="n">
-        <v>50.23</v>
+        <v>3.62</v>
       </c>
       <c r="O4" t="n">
-        <v>693901669000</v>
+        <v>38078746500</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>635000</v>
       </c>
       <c r="Q4" t="n">
-        <v>333000</v>
+        <v>52600</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 증시 및 반도체주 강세에 따른 SK하이닉스 주가 상승 기대감. 200만 돌파 및 500만원 목표 제시.</t>
+          <t>미국 증시 및 나스닥 폭등, 구리 가격 상승에 따른 주가 52주 신고가 경신 기대. 신고가 랠리 지속 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['미국증시', '반도체주', '목표가']</t>
+          <t>['신고가', '구리', 'AI']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>281500</v>
+        <v>18960</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.74%</t>
+          <t>'+3.66%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1</v>
+        <v>-0.27</v>
       </c>
       <c r="E5" t="n">
-        <v>673</v>
+        <v>43</v>
       </c>
       <c r="F5" t="n">
-        <v>427</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>3981</v>
+        <v>177</v>
       </c>
       <c r="H5" t="n">
-        <v>46.56</v>
+        <v>10.47</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>274000</v>
+        <v>18290</v>
       </c>
       <c r="K5" t="n">
-        <v>283000</v>
+        <v>18830</v>
       </c>
       <c r="L5" t="n">
-        <v>283500</v>
+        <v>19540</v>
       </c>
       <c r="M5" t="n">
-        <v>280000</v>
+        <v>18730</v>
       </c>
       <c r="N5" t="n">
-        <v>46.46</v>
+        <v>10.74</v>
       </c>
       <c r="O5" t="n">
-        <v>445118650250</v>
+        <v>45483479060</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q5" t="n">
-        <v>81100</v>
+        <v>3320</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -902,20 +902,20 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>3분기 영업이익 호조 및 30만 전자 돌파 기대감. 미 증시 반도체주 급등.</t>
+          <t>체코 원전 관련 건설 계약 기대감 및 공매도 관련 논의. 주가 상승에 대한 기대감 표출.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['영업이익', '반도체', '미증시']</t>
+          <t>['원전', '공매도', '건설']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,67 +924,67 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17890</v>
+        <v>1928000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.96%</t>
+          <t>'+3.21%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.68</v>
+        <v>-0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>74</v>
+        <v>554</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>356</v>
       </c>
       <c r="G6" t="n">
-        <v>309</v>
+        <v>2895</v>
       </c>
       <c r="H6" t="n">
-        <v>6.22</v>
+        <v>50.17</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>17720</v>
+        <v>1868000</v>
       </c>
       <c r="K6" t="n">
-        <v>18230</v>
+        <v>1909000</v>
       </c>
       <c r="L6" t="n">
-        <v>18750</v>
+        <v>1935000</v>
       </c>
       <c r="M6" t="n">
-        <v>17500</v>
+        <v>1904000</v>
       </c>
       <c r="N6" t="n">
-        <v>7.9</v>
+        <v>50.23</v>
       </c>
       <c r="O6" t="n">
-        <v>55524429405</v>
+        <v>894206236500</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>1272</v>
+        <v>333000</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -994,20 +994,20 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>AI 데이터 관련 낙관론 및 미국 광통신주 급등 수혜 기대. 코스닥 대장주 급등 출발.</t>
+          <t>미국 증시 및 반도체주 강세에 따른 주가 상승 기대감 고조. 200만 돌파 목표 및 장기적인 상승 전망 제시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '코스닥']</t>
+          <t>['반도체', 'AI', '나스닥']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>85800</v>
+        <v>281000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.59%</t>
+          <t>'+2.55%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E7" t="n">
-        <v>99</v>
+        <v>708</v>
       </c>
       <c r="F7" t="n">
-        <v>68</v>
+        <v>441</v>
       </c>
       <c r="G7" t="n">
-        <v>463</v>
+        <v>4044</v>
       </c>
       <c r="H7" t="n">
-        <v>23.05</v>
+        <v>46.56</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,28 +1055,28 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>85300</v>
+        <v>274000</v>
       </c>
       <c r="K7" t="n">
-        <v>87000</v>
+        <v>283000</v>
       </c>
       <c r="L7" t="n">
-        <v>87000</v>
+        <v>283500</v>
       </c>
       <c r="M7" t="n">
-        <v>85500</v>
+        <v>280000</v>
       </c>
       <c r="N7" t="n">
-        <v>23.12</v>
+        <v>46.46</v>
       </c>
       <c r="O7" t="n">
-        <v>30178877800</v>
+        <v>596271758000</v>
       </c>
       <c r="P7" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>57000</v>
+        <v>81100</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1086,27 +1086,211 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 SMR 사업 추진 확정 및 공급 계약 체결. 차세대 KDDX 전기추진 시스템 공급 계약.</t>
+          <t>3분기 영업이익 호조 및 30만 전자 돌파 기대감. 미 증시 반도체주 급등.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['SMR', '공급 계약', 'KDDX']</t>
+          <t>['영업이익', '반도체', '미증시']</t>
         </is>
       </c>
       <c r="X7" t="n">
+        <v>111</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>17950</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'+1.30%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="E8" t="n">
+        <v>90</v>
+      </c>
+      <c r="F8" t="n">
+        <v>61</v>
+      </c>
+      <c r="G8" t="n">
+        <v>358</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>17720</v>
+      </c>
+      <c r="K8" t="n">
+        <v>18230</v>
+      </c>
+      <c r="L8" t="n">
+        <v>18750</v>
+      </c>
+      <c r="M8" t="n">
+        <v>17500</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O8" t="n">
+        <v>76292352945</v>
+      </c>
+      <c r="P8" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1272</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>미국 광통신주 강세 및 AI 데이터 관련 낙관론에 따른 주가 상승 기대. 단기 급등 및 숏커버 가능성 언급.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['광통신', 'AI', '숏커버']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>86200</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'+1.06%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>105</v>
+      </c>
+      <c r="F9" t="n">
+        <v>70</v>
+      </c>
+      <c r="G9" t="n">
+        <v>489</v>
+      </c>
+      <c r="H9" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>85300</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>87000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>85500</v>
+      </c>
+      <c r="N9" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="O9" t="n">
+        <v>36459083450</v>
+      </c>
+      <c r="P9" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>SMR 사업 추진 확정 및 미국 레오나르도 DRS와의 공급 계약 체결 관련 긍정적 언급. 외인 공매도 조사 필요성 제기.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['SMR', '공급계약', '공매도']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
         <v>19</v>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>034020</t>
         </is>

--- a/data/trending_integrated_20260922_09.xlsx
+++ b/data/trending_integrated_20260922_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63600</v>
+        <v>65100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+21.61%</t>
+          <t>'+24.71%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -584,7 +584,7 @@
         <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H2" t="n">
         <v>6.87</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>52300</v>
+        <v>52200</v>
       </c>
       <c r="K2" t="n">
-        <v>60800</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>65700</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>59700</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>6.88</v>
       </c>
       <c r="O2" t="n">
-        <v>43627337200</v>
+        <v>52071000000</v>
       </c>
       <c r="P2" t="n">
-        <v>148300</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16300</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>SK하이닉스의 GDDR7 기판 공급망 합류 관련 뉴스 기반 주가 상승 기대. 일부 매도 의견 혼재.</t>
+          <t>SK하이닉스 GDDR7 기판 공급망 합류 뉴스 기반 주가 급등. 고점 매도 및 장기 투자 논쟁.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['GDDR7', '반도체', '기판']</t>
+          <t>['GDDR7', '기판', '공급망']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6340</v>
+        <v>6270</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+8.19%</t>
+          <t>'+12.77%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.19</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>5860</v>
+        <v>5560</v>
       </c>
       <c r="K3" t="n">
-        <v>6200</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>6610</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>6150</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0.19</v>
       </c>
       <c r="O3" t="n">
-        <v>28193598825</v>
+        <v>30624000000</v>
       </c>
       <c r="P3" t="n">
-        <v>13140</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3725</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,12 +718,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>비트코인 급등 및 가상화폐 테마 강세에 따른 주가 상승 전망. 공매도 관련 언급.</t>
+          <t>비트코인 급등에 따른 가상화폐 테마주 강세. 공매도 세력에 대한 강한 불만 표출.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>332500</v>
+        <v>281000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+4.40%</t>
+          <t>'+8.08%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>52</v>
+        <v>714</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>452</v>
       </c>
       <c r="G4" t="n">
-        <v>140</v>
+        <v>4062</v>
       </c>
       <c r="H4" t="n">
-        <v>3.22</v>
+        <v>46.56</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>318500</v>
+        <v>260000</v>
       </c>
       <c r="K4" t="n">
-        <v>333000</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>342000</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>325000</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.62</v>
+        <v>46.46</v>
       </c>
       <c r="O4" t="n">
-        <v>38078746500</v>
+        <v>812832000000</v>
       </c>
       <c r="P4" t="n">
-        <v>635000</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>52600</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -810,20 +810,20 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 증시 및 나스닥 폭등, 구리 가격 상승에 따른 주가 52주 신고가 경신 기대. 신고가 랠리 지속 전망.</t>
+          <t>3분기 영업이익 호조 및 30만 전자 돌파 기대감. 미 증시 반도체주 급등.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['신고가', '구리', 'AI']</t>
+          <t>['영업이익', '반도체', '미증시']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18960</v>
+        <v>32600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.66%</t>
+          <t>'+3.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.27</v>
+        <v>-0.62</v>
       </c>
       <c r="E5" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>177</v>
+        <v>68</v>
       </c>
       <c r="H5" t="n">
-        <v>10.47</v>
+        <v>11.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>18290</v>
+        <v>31650</v>
       </c>
       <c r="K5" t="n">
-        <v>18830</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>19540</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>18730</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>10.74</v>
+        <v>11.92</v>
       </c>
       <c r="O5" t="n">
-        <v>45483479060</v>
+        <v>138630000000</v>
       </c>
       <c r="P5" t="n">
-        <v>40350</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3320</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -902,20 +902,20 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>체코 원전 관련 건설 계약 기대감 및 공매도 관련 논의. 주가 상승에 대한 기대감 표출.</t>
+          <t>가온전선 신고가 경신 대비 대한전선 주가 부진. 4분기 이후 전력 인프라 테마 부상 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '건설']</t>
+          <t>['전력인프라', '테마', '주가']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1928000</v>
+        <v>1879000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.21%</t>
+          <t>'+1.62%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>554</v>
+        <v>583</v>
       </c>
       <c r="F6" t="n">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="G6" t="n">
-        <v>2895</v>
+        <v>2959</v>
       </c>
       <c r="H6" t="n">
         <v>50.17</v>
@@ -963,28 +963,28 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1868000</v>
+        <v>1849000</v>
       </c>
       <c r="K6" t="n">
-        <v>1909000</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1935000</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1904000</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>50.23</v>
       </c>
       <c r="O6" t="n">
-        <v>894206236500</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>333000</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 증시 및 반도체주 강세에 따른 주가 상승 기대감 고조. 200만 돌파 목표 및 장기적인 상승 전망 제시.</t>
+          <t>AI 관련주 강세 및 미국 증시 폭등에 따른 SK하이닉스 주가 상승 기대감 고조. 200만 돌파 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반도체', 'AI', '나스닥']</t>
+          <t>['AI', '미국증시', '주가상승']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>281000</v>
+        <v>326000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.55%</t>
+          <t>'+1.24%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>708</v>
+        <v>62</v>
       </c>
       <c r="F7" t="n">
-        <v>441</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>4044</v>
+        <v>148</v>
       </c>
       <c r="H7" t="n">
-        <v>46.56</v>
+        <v>3.22</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,28 +1055,28 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>274000</v>
+        <v>322000</v>
       </c>
       <c r="K7" t="n">
-        <v>283000</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>283500</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>280000</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>46.46</v>
+        <v>3.62</v>
       </c>
       <c r="O7" t="n">
-        <v>596271758000</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>81100</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1086,20 +1086,20 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>3분기 영업이익 호조 및 30만 전자 돌파 기대감. 미 증시 반도체주 급등.</t>
+          <t>미국 증시 폭등 및 변압기 관련주 강세 속 가온전선 신고가 경신 기대. 구리 가격 상승 요인.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['영업이익', '반도체', '미증시']</t>
+          <t>['신고가', '변압기', '구리']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,67 +1108,67 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17950</v>
+        <v>86500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.30%</t>
+          <t>'+0.93%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.68</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="F8" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="G8" t="n">
-        <v>358</v>
+        <v>513</v>
       </c>
       <c r="H8" t="n">
-        <v>6.22</v>
+        <v>23.05</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>17720</v>
+        <v>85700</v>
       </c>
       <c r="K8" t="n">
-        <v>18230</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>18750</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>17500</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>7.9</v>
+        <v>23.12</v>
       </c>
       <c r="O8" t="n">
-        <v>76292352945</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1272</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 광통신주 강세 및 AI 데이터 관련 낙관론에 따른 주가 상승 기대. 단기 급등 및 숏커버 가능성 언급.</t>
+          <t>SMR 사업 추진 확정 및 미국 레오나르도 DRS와의 공급 계약 체결 관련 긍정적 언급. 외인 공매도 조사 필요성 제기.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '숏커버']</t>
+          <t>['SMR', '공급계약', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86200</v>
+        <v>18690</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.06%</t>
+          <t>'-1.74%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.27</v>
       </c>
       <c r="E9" t="n">
-        <v>105</v>
+        <v>56</v>
       </c>
       <c r="F9" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>489</v>
+        <v>207</v>
       </c>
       <c r="H9" t="n">
-        <v>23.05</v>
+        <v>10.47</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,28 +1239,28 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>85300</v>
+        <v>19020</v>
       </c>
       <c r="K9" t="n">
-        <v>87000</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>87000</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>85500</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>23.12</v>
+        <v>10.74</v>
       </c>
       <c r="O9" t="n">
-        <v>36459083450</v>
+        <v>54969000000</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1270,20 +1270,20 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SMR 사업 추진 확정 및 미국 레오나르도 DRS와의 공급 계약 체결 관련 긍정적 언급. 외인 공매도 조사 필요성 제기.</t>
+          <t>체코 원전 관련 수주 기대감 속 공매도 및 단기 매매 세력에 대한 불만 토로.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['SMR', '공급계약', '공매도']</t>
+          <t>['체코원전', '공매도', '수주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,283 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>17890</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-2.77%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="E10" t="n">
+        <v>99</v>
+      </c>
+      <c r="F10" t="n">
+        <v>65</v>
+      </c>
+      <c r="G10" t="n">
+        <v>393</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>18400</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O10" t="n">
+        <v>85674000000</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>미국 광통신주 강세에 따른 대한광통신 주가 상승 기대. AI 데이터 낙관론 부각.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['광통신', 'AI', '주가상승']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>광전자</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10260</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-2.84%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F11" t="n">
+        <v>35</v>
+      </c>
+      <c r="G11" t="n">
+        <v>112</v>
+      </c>
+      <c r="H11" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>10560</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="O11" t="n">
+        <v>17478000000</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>투자경고 종목 지정 및 주가 하락에 대한 부정적 전망. 잡주로 평가 절하.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['투자경고', '주가하락', '잡주']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>017900</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>미투온</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3905</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-6.47%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E12" t="n">
+        <v>42</v>
+      </c>
+      <c r="F12" t="n">
+        <v>33</v>
+      </c>
+      <c r="G12" t="n">
+        <v>162</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>4175</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4257000000</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>비트코인 강세에도 불구하고 미투온 주가 부진. 투자자 간 극명한 시각 차이.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['비트코인', '주가부진', '차트분석']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>201490</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260922_09.xlsx
+++ b/data/trending_integrated_20260922_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>65100</v>
+        <v>67900</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+24.71%</t>
+          <t>'+29.83%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F2" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H2" t="n">
         <v>6.87</v>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>52200</v>
+        <v>52300</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>60800</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>67900</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>59700</v>
       </c>
       <c r="N2" t="n">
         <v>6.88</v>
       </c>
       <c r="O2" t="n">
-        <v>52071000000</v>
+        <v>71673170750</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>148300</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>16300</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-46000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>SK하이닉스 GDDR7 기판 공급망 합류 뉴스 기반 주가 급등. 고점 매도 및 장기 투자 논쟁.</t>
+          <t>SK하이닉스 공급망 합류 뉴스 기반 키 맞추기 및 단기 급등 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['GDDR7', '기판', '공급망']</t>
+          <t>['SK하이닉스', '기판', '공급망']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6270</v>
+        <v>32400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.77%</t>
+          <t>'+9.09%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.19</v>
+        <v>-0.62</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>5560</v>
+        <v>29700</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>30500</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>33450</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="N3" t="n">
-        <v>0.19</v>
+        <v>11.92</v>
       </c>
       <c r="O3" t="n">
-        <v>30624000000</v>
+        <v>161722204525</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>75900</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>143000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>비트코인 급등에 따른 가상화폐 테마주 강세. 공매도 세력에 대한 강한 불만 표출.</t>
+          <t>전선주 내 가온전선과의 비교 언급. 4분기 이후 전력 인프라 테마 전환 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['비트코인', '가상화폐', '공매도']</t>
+          <t>['전선주', '인프라', '테마']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>281000</v>
+        <v>6310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.08%</t>
+          <t>'+7.68%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="E4" t="n">
-        <v>714</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
-        <v>452</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>4062</v>
+        <v>99</v>
       </c>
       <c r="H4" t="n">
-        <v>46.56</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>260000</v>
+        <v>5860</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>6610</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>6150</v>
       </c>
       <c r="N4" t="n">
-        <v>46.46</v>
+        <v>0.19</v>
       </c>
       <c r="O4" t="n">
-        <v>812832000000</v>
+        <v>33118094600</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>13140</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3725</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>356000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>3분기 영업이익 호조 및 30만 전자 돌파 기대감. 미 증시 반도체주 급등.</t>
+          <t>비트코인 및 가상화폐 테마 급등에 따른 관련주 동반 상승 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['영업이익', '반도체', '미증시']</t>
+          <t>['비트코인', '가상화폐', '테마']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32600</v>
+        <v>337000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.00%</t>
+          <t>'+5.81%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.62</v>
+        <v>-0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
-        <v>68</v>
+        <v>176</v>
       </c>
       <c r="H5" t="n">
-        <v>11.3</v>
+        <v>3.22</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>31650</v>
+        <v>318500</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>333000</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>349500</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>325000</v>
       </c>
       <c r="N5" t="n">
-        <v>11.92</v>
+        <v>3.62</v>
       </c>
       <c r="O5" t="n">
-        <v>138630000000</v>
+        <v>78794192250</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>635000</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>52600</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>가온전선 신고가 경신 대비 대한전선 주가 부진. 4분기 이후 전력 인프라 테마 부상 기대.</t>
+          <t>구리 가격 상승 및 신고가 랠리에 따른 가온전선 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['전력인프라', '테마', '주가']</t>
+          <t>['구리', '신고가', '주가']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1879000</v>
+        <v>1932000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.62%</t>
+          <t>'+3.43%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>583</v>
+        <v>617</v>
       </c>
       <c r="F6" t="n">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="G6" t="n">
-        <v>2959</v>
+        <v>2999</v>
       </c>
       <c r="H6" t="n">
         <v>50.17</v>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1849000</v>
+        <v>1868000</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1909000</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1935000</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1904000</v>
       </c>
       <c r="N6" t="n">
         <v>50.23</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1231410924500</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>333000</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>81000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>AI 관련주 강세 및 미국 증시 폭등에 따른 SK하이닉스 주가 상승 기대감 고조. 200만 돌파 전망.</t>
+          <t>AI 반도체 주 강세 및 뉴욕 증시 급등에 따른 SK하이닉스 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['AI', '미국증시', '주가상승']</t>
+          <t>['AI', '반도체', '뉴욕증시']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>326000</v>
+        <v>281250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.24%</t>
+          <t>'+2.65%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E7" t="n">
-        <v>62</v>
+        <v>740</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>466</v>
       </c>
       <c r="G7" t="n">
-        <v>148</v>
+        <v>4156</v>
       </c>
       <c r="H7" t="n">
-        <v>3.22</v>
+        <v>46.56</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>322000</v>
+        <v>274000</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>283000</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>283500</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>279500</v>
       </c>
       <c r="N7" t="n">
-        <v>3.62</v>
+        <v>46.46</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>941363575250</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>81100</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-246000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 증시 폭등 및 변압기 관련주 강세 속 가온전선 신고가 경신 기대. 구리 가격 상승 요인.</t>
+          <t>3분기 영업이익 호조 및 30만 전자 돌파 기대감. 미 증시 반도체주 급등.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['신고가', '변압기', '구리']</t>
+          <t>['영업이익', '반도체', '미증시']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86500</v>
+        <v>18580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.93%</t>
+          <t>'+1.59%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.27</v>
       </c>
       <c r="E8" t="n">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="F8" t="n">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>513</v>
+        <v>242</v>
       </c>
       <c r="H8" t="n">
-        <v>23.05</v>
+        <v>10.47</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>85700</v>
+        <v>18290</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>18830</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>19540</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>18570</v>
       </c>
       <c r="N8" t="n">
-        <v>23.12</v>
+        <v>10.74</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>61337278800</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>184000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>SMR 사업 추진 확정 및 미국 레오나르도 DRS와의 공급 계약 체결 관련 긍정적 언급. 외인 공매도 조사 필요성 제기.</t>
+          <t>체코 원전 관련 시멘트 계약 언급 및 공매도 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['SMR', '공급계약', '공매도']</t>
+          <t>['원전', '공매도', '계약']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18690</v>
+        <v>86000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.74%</t>
+          <t>'+0.82%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.27</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="G9" t="n">
-        <v>207</v>
+        <v>523</v>
       </c>
       <c r="H9" t="n">
-        <v>10.47</v>
+        <v>23.05</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>19020</v>
+        <v>85300</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>87000</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>87000</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>85500</v>
       </c>
       <c r="N9" t="n">
-        <v>10.74</v>
+        <v>23.12</v>
       </c>
       <c r="O9" t="n">
-        <v>54969000000</v>
+        <v>43226693700</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>139200</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-103000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>체코 원전 관련 수주 기대감 속 공매도 및 단기 매매 세력에 대한 불만 토로.</t>
+          <t>미국 SMR 투자 확정 및 전기추진 시스템 공급 계약 관련 긍정적 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['체코원전', '공매도', '수주']</t>
+          <t>['SMR', '투자', '계약']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17890</v>
+        <v>17830</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.77%</t>
+          <t>'+0.62%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-1.68</v>
       </c>
       <c r="E10" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F10" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G10" t="n">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="H10" t="n">
         <v>6.22</v>
@@ -1331,31 +1331,31 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18400</v>
+        <v>17720</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>18230</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>18750</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>17500</v>
       </c>
       <c r="N10" t="n">
         <v>7.9</v>
       </c>
       <c r="O10" t="n">
-        <v>85674000000</v>
+        <v>92409284755</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-288000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10260</v>
+        <v>8535</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.84%</t>
+          <t>'+0.18%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.4</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H11" t="n">
-        <v>17.89</v>
+        <v>26.58</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10560</v>
+        <v>8520</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>8620</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>8650</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>8460</v>
       </c>
       <c r="N11" t="n">
-        <v>18.29</v>
+        <v>26.57</v>
       </c>
       <c r="O11" t="n">
-        <v>17478000000</v>
+        <v>6883930495</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>17950</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>8120</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-99000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>투자경고 종목 지정 및 주가 하락에 대한 부정적 전망. 잡주로 평가 절하.</t>
+          <t>반도체 업황 부진 속에서 LG디스플레이의 장기 소외 및 주가 부진 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['투자경고', '주가하락', '잡주']</t>
+          <t>['반도체', '장기소외', '주가']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3905</v>
+        <v>3890</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-6.47%</t>
+          <t>'-4.07%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.63</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G12" t="n">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="H12" t="n">
         <v>0.96</v>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4175</v>
+        <v>4055</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>4080</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4080</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3850</v>
       </c>
       <c r="N12" t="n">
         <v>0.33</v>
       </c>
       <c r="O12" t="n">
-        <v>4257000000</v>
+        <v>4980428085</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>6480</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1738</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-52000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>비트코인 강세에도 불구하고 미투온 주가 부진. 투자자 간 극명한 시각 차이.</t>
+          <t>비트코인 가격 회복에 따른 기대감 및 인수 관련 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['비트코인', '주가부진', '차트분석']</t>
+          <t>['비트코인', '인수', '기대감']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1569,6 +1569,98 @@
       <c r="Z12" t="inlineStr">
         <is>
           <t>201490</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>광전자</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10470</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>'-5.33%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>51</v>
+      </c>
+      <c r="F13" t="n">
+        <v>37</v>
+      </c>
+      <c r="G13" t="n">
+        <v>121</v>
+      </c>
+      <c r="H13" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>11060</v>
+      </c>
+      <c r="K13" t="n">
+        <v>10570</v>
+      </c>
+      <c r="L13" t="n">
+        <v>10680</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10060</v>
+      </c>
+      <c r="N13" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="O13" t="n">
+        <v>20046037525</v>
+      </c>
+      <c r="P13" t="n">
+        <v>22450</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1760</v>
+      </c>
+      <c r="R13" t="n">
+        <v>29000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>투자경고 종목 지정 관련 내용 및 주가 하락에 대한 부정적 전망.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['투자경고', '주가', '전망']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>017900</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260922_09.xlsx
+++ b/data/trending_integrated_20260922_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,70 +563,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>67900</v>
+        <v>2885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+29.83%</t>
+          <t>'+29.95%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.01</v>
+        <v>-0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="H2" t="n">
-        <v>6.87</v>
+        <v>0.48</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>52300</v>
+        <v>2220</v>
       </c>
       <c r="K2" t="n">
-        <v>60800</v>
+        <v>2410</v>
       </c>
       <c r="L2" t="n">
-        <v>67900</v>
+        <v>2885</v>
       </c>
       <c r="M2" t="n">
-        <v>59700</v>
+        <v>2410</v>
       </c>
       <c r="N2" t="n">
-        <v>6.88</v>
+        <v>0.7</v>
       </c>
       <c r="O2" t="n">
-        <v>71673170750</v>
+        <v>5163902209</v>
       </c>
       <c r="P2" t="n">
-        <v>148300</v>
+        <v>4760</v>
       </c>
       <c r="Q2" t="n">
-        <v>16300</v>
+        <v>973</v>
       </c>
       <c r="R2" t="n">
-        <v>-46000</v>
+        <v>63000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>SK하이닉스 공급망 합류 뉴스 기반 키 맞추기 및 단기 급등 기대.</t>
+          <t>악재 해소 및 기관 투자자, 공매도 상환 가격에 대한 분석. 휴니버스 글로벌과의 시너지 및 클라우드 백신 허브 기대감 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '기판', '공급망']</t>
+          <t>['기관 투자자', '공매도', '클라우드 백신']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32400</v>
+        <v>66800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.09%</t>
+          <t>'+27.72%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.62</v>
+        <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G3" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H3" t="n">
-        <v>11.3</v>
+        <v>6.87</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>29700</v>
+        <v>52300</v>
       </c>
       <c r="K3" t="n">
-        <v>30500</v>
+        <v>60800</v>
       </c>
       <c r="L3" t="n">
-        <v>33450</v>
+        <v>67900</v>
       </c>
       <c r="M3" t="n">
-        <v>30000</v>
+        <v>59700</v>
       </c>
       <c r="N3" t="n">
-        <v>11.92</v>
+        <v>6.88</v>
       </c>
       <c r="O3" t="n">
-        <v>161722204525</v>
+        <v>98552038750</v>
       </c>
       <c r="P3" t="n">
-        <v>75900</v>
+        <v>148300</v>
       </c>
       <c r="Q3" t="n">
-        <v>15000</v>
+        <v>16300</v>
       </c>
       <c r="R3" t="n">
-        <v>143000</v>
+        <v>-46000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>전선주 내 가온전선과의 비교 언급. 4분기 이후 전력 인프라 테마 전환 기대.</t>
+          <t>심텍과의 비교를 통해 코리아써키트의 키 맞추기 상승 기대감 표출. 반도체 관련 뉴스를 호재로 언급하며 단기 상승 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['전선주', '인프라', '테마']</t>
+          <t>['키 맞추기', '반도체']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6310</v>
+        <v>6470</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.68%</t>
+          <t>'+10.41%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.19</v>
       </c>
       <c r="E4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F4" t="n">
         <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0.19</v>
       </c>
       <c r="O4" t="n">
-        <v>33118094600</v>
+        <v>39725561975</v>
       </c>
       <c r="P4" t="n">
         <v>13140</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>비트코인 및 가상화폐 테마 급등에 따른 관련주 동반 상승 기대.</t>
+          <t>비트코인 급등 및 가상화폐 테마 강세에 따른 우리기술투자의 상승 기대감 표출. 공개매수 및 공매도 세력과의 대립 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['비트코인', '가상화폐', '테마']</t>
+          <t>['비트코인', '가상화폐 테마', '공매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>337000</v>
+        <v>32450</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.81%</t>
+          <t>'+9.26%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.4</v>
+        <v>-0.62</v>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="H5" t="n">
-        <v>3.22</v>
+        <v>11.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>318500</v>
+        <v>29700</v>
       </c>
       <c r="K5" t="n">
-        <v>333000</v>
+        <v>30500</v>
       </c>
       <c r="L5" t="n">
-        <v>349500</v>
+        <v>33450</v>
       </c>
       <c r="M5" t="n">
-        <v>325000</v>
+        <v>30000</v>
       </c>
       <c r="N5" t="n">
-        <v>3.62</v>
+        <v>11.92</v>
       </c>
       <c r="O5" t="n">
-        <v>78794192250</v>
+        <v>172721334675</v>
       </c>
       <c r="P5" t="n">
-        <v>635000</v>
+        <v>75900</v>
       </c>
       <c r="Q5" t="n">
-        <v>52600</v>
+        <v>15000</v>
       </c>
       <c r="R5" t="n">
-        <v>7000</v>
+        <v>143000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>구리 가격 상승 및 신고가 랠리에 따른 가온전선 주가 상승 기대.</t>
+          <t>가온전선과의 비교 속에서 대한전선의 상승 기대감 표출. 4분기 이후 전력 인프라 중심으로 시장 관심 이동 전망. 유증 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['구리', '신고가', '주가']</t>
+          <t>['전력 인프라', '유증']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1932000</v>
+        <v>334000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.43%</t>
+          <t>'+4.87%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.06</v>
+        <v>-0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>617</v>
+        <v>75</v>
       </c>
       <c r="F6" t="n">
-        <v>386</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>2999</v>
+        <v>184</v>
       </c>
       <c r="H6" t="n">
-        <v>50.17</v>
+        <v>3.22</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1868000</v>
+        <v>318500</v>
       </c>
       <c r="K6" t="n">
-        <v>1909000</v>
+        <v>333000</v>
       </c>
       <c r="L6" t="n">
-        <v>1935000</v>
+        <v>349500</v>
       </c>
       <c r="M6" t="n">
-        <v>1904000</v>
+        <v>325000</v>
       </c>
       <c r="N6" t="n">
-        <v>50.23</v>
+        <v>3.62</v>
       </c>
       <c r="O6" t="n">
-        <v>1231410924500</v>
+        <v>82469267000</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>635000</v>
       </c>
       <c r="Q6" t="n">
-        <v>333000</v>
+        <v>52600</v>
       </c>
       <c r="R6" t="n">
-        <v>81000</v>
+        <v>7000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>AI 반도체 주 강세 및 뉴욕 증시 급등에 따른 SK하이닉스 주가 상승 기대.</t>
+          <t>나스닥 폭등 및 외인 지분율 상승에 따른 가온전선 신고가 경신 기대감 표출. 구리 가격 상승과 성장 동력 강조.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '뉴욕증시']</t>
+          <t>['신고가', '구리 가격', '성장 동력']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>281250</v>
+        <v>1925000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.65%</t>
+          <t>'+3.05%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>740</v>
+        <v>653</v>
       </c>
       <c r="F7" t="n">
-        <v>466</v>
+        <v>401</v>
       </c>
       <c r="G7" t="n">
-        <v>4156</v>
+        <v>3084</v>
       </c>
       <c r="H7" t="n">
-        <v>46.56</v>
+        <v>50.17</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>274000</v>
+        <v>1868000</v>
       </c>
       <c r="K7" t="n">
-        <v>283000</v>
+        <v>1909000</v>
       </c>
       <c r="L7" t="n">
-        <v>283500</v>
+        <v>1935000</v>
       </c>
       <c r="M7" t="n">
-        <v>279500</v>
+        <v>1904000</v>
       </c>
       <c r="N7" t="n">
-        <v>46.46</v>
+        <v>50.23</v>
       </c>
       <c r="O7" t="n">
-        <v>941363575250</v>
+        <v>1349752448500</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>81100</v>
+        <v>333000</v>
       </c>
       <c r="R7" t="n">
-        <v>-246000</v>
+        <v>81000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>3분기 영업이익 호조 및 30만 전자 돌파 기대감. 미 증시 반도체주 급등.</t>
+          <t>AI 반도체 주 강세 및 뉴욕 증시 급등에 따른 SK하이닉스 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['영업이익', '반도체', '미증시']</t>
+          <t>['AI', '반도체', '뉴욕증시']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18580</v>
+        <v>280750</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.59%</t>
+          <t>'+2.46%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.27</v>
+        <v>0.1</v>
       </c>
       <c r="E8" t="n">
-        <v>62</v>
+        <v>748</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>472</v>
       </c>
       <c r="G8" t="n">
-        <v>242</v>
+        <v>4204</v>
       </c>
       <c r="H8" t="n">
-        <v>10.47</v>
+        <v>46.56</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18290</v>
+        <v>274000</v>
       </c>
       <c r="K8" t="n">
-        <v>18830</v>
+        <v>283000</v>
       </c>
       <c r="L8" t="n">
-        <v>19540</v>
+        <v>283500</v>
       </c>
       <c r="M8" t="n">
-        <v>18570</v>
+        <v>279500</v>
       </c>
       <c r="N8" t="n">
-        <v>10.74</v>
+        <v>46.46</v>
       </c>
       <c r="O8" t="n">
-        <v>61337278800</v>
+        <v>1059843221750</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>81100</v>
       </c>
       <c r="R8" t="n">
-        <v>184000</v>
+        <v>-246000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>체코 원전 관련 시멘트 계약 언급 및 공매도 관련 부정적 언급.</t>
+          <t>3분기 영업이익 호조 및 30만 전자 돌파 기대감. 미 증시 반도체주 급등.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '계약']</t>
+          <t>['영업이익', '반도체', '미증시']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86000</v>
+        <v>18700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.82%</t>
+          <t>'+2.24%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.27</v>
       </c>
       <c r="E9" t="n">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="F9" t="n">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="G9" t="n">
-        <v>523</v>
+        <v>284</v>
       </c>
       <c r="H9" t="n">
-        <v>23.05</v>
+        <v>10.47</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>85300</v>
+        <v>18290</v>
       </c>
       <c r="K9" t="n">
-        <v>87000</v>
+        <v>18830</v>
       </c>
       <c r="L9" t="n">
-        <v>87000</v>
+        <v>19540</v>
       </c>
       <c r="M9" t="n">
-        <v>85500</v>
+        <v>18560</v>
       </c>
       <c r="N9" t="n">
-        <v>23.12</v>
+        <v>10.74</v>
       </c>
       <c r="O9" t="n">
-        <v>43226693700</v>
+        <v>64436156850</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>-103000</v>
+        <v>184000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 SMR 투자 확정 및 전기추진 시스템 공급 계약 관련 긍정적 언급.</t>
+          <t>공매도 세력에 대한 비판과 함께 주가 상승 기대감 표출. 체코 원전 관련 수주 및 계약 마무리 기대감 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['SMR', '투자', '계약']</t>
+          <t>['공매도', '체코 원전']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17830</v>
+        <v>86200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.62%</t>
+          <t>'+1.06%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.68</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="F10" t="n">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="G10" t="n">
-        <v>412</v>
+        <v>553</v>
       </c>
       <c r="H10" t="n">
-        <v>6.22</v>
+        <v>23.05</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17720</v>
+        <v>85300</v>
       </c>
       <c r="K10" t="n">
-        <v>18230</v>
+        <v>87000</v>
       </c>
       <c r="L10" t="n">
-        <v>18750</v>
+        <v>87000</v>
       </c>
       <c r="M10" t="n">
-        <v>17500</v>
+        <v>85500</v>
       </c>
       <c r="N10" t="n">
-        <v>7.9</v>
+        <v>23.12</v>
       </c>
       <c r="O10" t="n">
-        <v>92409284755</v>
+        <v>47471282050</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>1272</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>-288000</v>
+        <v>-103000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 광통신주 강세에 따른 대한광통신 주가 상승 기대. AI 데이터 낙관론 부각.</t>
+          <t>미국 SMR 및 KDDX 관련 공급 계약 체결로 인한 주가 상승 기대감 표출. 드러켄밀러 회장 방문 가능성 언급 및 공매도 조사 촉구.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '주가상승']</t>
+          <t>['SMR', 'KDDX', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8535</v>
+        <v>17730</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.18%</t>
+          <t>'+0.06%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>-1.68</v>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="G11" t="n">
-        <v>110</v>
+        <v>428</v>
       </c>
       <c r="H11" t="n">
-        <v>26.58</v>
+        <v>6.22</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8520</v>
+        <v>17720</v>
       </c>
       <c r="K11" t="n">
-        <v>8620</v>
+        <v>18230</v>
       </c>
       <c r="L11" t="n">
-        <v>8650</v>
+        <v>18750</v>
       </c>
       <c r="M11" t="n">
-        <v>8460</v>
+        <v>17500</v>
       </c>
       <c r="N11" t="n">
-        <v>26.57</v>
+        <v>7.9</v>
       </c>
       <c r="O11" t="n">
-        <v>6883930495</v>
+        <v>98774141880</v>
       </c>
       <c r="P11" t="n">
-        <v>17950</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>8120</v>
+        <v>1272</v>
       </c>
       <c r="R11" t="n">
-        <v>-99000</v>
+        <v>-288000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>반도체 업황 부진 속에서 LG디스플레이의 장기 소외 및 주가 부진 우려.</t>
+          <t>미국 광통신 기업들의 동반 상승에 따른 대한광통신 주가 상승 기대감 표출. AI 데이터 관련 낙관론 및 메타 관련 호재 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', '장기소외', '주가']</t>
+          <t>['광통신', 'AI 데이터', '메타']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3890</v>
+        <v>8510</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.07%</t>
+          <t>'-0.12%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.63</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G12" t="n">
-        <v>190</v>
+        <v>127</v>
       </c>
       <c r="H12" t="n">
-        <v>0.96</v>
+        <v>26.58</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4055</v>
+        <v>8520</v>
       </c>
       <c r="K12" t="n">
-        <v>4080</v>
+        <v>8620</v>
       </c>
       <c r="L12" t="n">
-        <v>4080</v>
+        <v>8650</v>
       </c>
       <c r="M12" t="n">
-        <v>3850</v>
+        <v>8460</v>
       </c>
       <c r="N12" t="n">
-        <v>0.33</v>
+        <v>26.57</v>
       </c>
       <c r="O12" t="n">
-        <v>4980428085</v>
+        <v>7547508195</v>
       </c>
       <c r="P12" t="n">
-        <v>6480</v>
+        <v>17950</v>
       </c>
       <c r="Q12" t="n">
-        <v>1738</v>
+        <v>8120</v>
       </c>
       <c r="R12" t="n">
-        <v>-52000</v>
+        <v>-99000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>비트코인 가격 회복에 따른 기대감 및 인수 관련 언급.</t>
+          <t>반도체 업황 부진 및 회사의 무능함에 대한 비판. 장기 소외주로 분류하며 부정적 전망. 대차잔고 감소는 긍정적 요소로 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['비트코인', '인수', '기대감']</t>
+          <t>['반도체', '장기 소외주']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,97 +1568,189 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10470</v>
+        <v>3980</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.33%</t>
+          <t>'-1.85%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.4</v>
+        <v>0.63</v>
       </c>
       <c r="E13" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>121</v>
+        <v>197</v>
       </c>
       <c r="H13" t="n">
-        <v>17.89</v>
+        <v>0.96</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>11060</v>
+        <v>4055</v>
       </c>
       <c r="K13" t="n">
-        <v>10570</v>
+        <v>4080</v>
       </c>
       <c r="L13" t="n">
-        <v>10680</v>
+        <v>4080</v>
       </c>
       <c r="M13" t="n">
-        <v>10060</v>
+        <v>3850</v>
       </c>
       <c r="N13" t="n">
-        <v>18.29</v>
+        <v>0.33</v>
       </c>
       <c r="O13" t="n">
-        <v>20046037525</v>
+        <v>6298597000</v>
       </c>
       <c r="P13" t="n">
-        <v>22450</v>
+        <v>6480</v>
       </c>
       <c r="Q13" t="n">
-        <v>1760</v>
+        <v>1738</v>
       </c>
       <c r="R13" t="n">
-        <v>29000</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>투자경고 종목 지정 관련 내용 및 주가 하락에 대한 부정적 전망.</t>
+          <t>비트코인 가격 회복에 따른 기대감 및 인수 관련 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['비트코인', '인수', '기대감']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>201490</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>광전자</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>10440</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'-5.61%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>58</v>
+      </c>
+      <c r="F14" t="n">
+        <v>40</v>
+      </c>
+      <c r="G14" t="n">
+        <v>128</v>
+      </c>
+      <c r="H14" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>11060</v>
+      </c>
+      <c r="K14" t="n">
+        <v>10570</v>
+      </c>
+      <c r="L14" t="n">
+        <v>10680</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10060</v>
+      </c>
+      <c r="N14" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="O14" t="n">
+        <v>21391983630</v>
+      </c>
+      <c r="P14" t="n">
+        <v>22450</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1760</v>
+      </c>
+      <c r="R14" t="n">
+        <v>29000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>주가 하락 및 투자 경고 종목 지정에 대한 불만 표출. 미래 먹거리 관련 기대감은 있으나 구체적 근거 부족.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
         <v>0.1</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>['투자경고', '주가', '전망']</t>
-        </is>
-      </c>
-      <c r="X13" t="n">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['투자 경고', '미래 먹거리']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
         <v>7</v>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>017900</t>
         </is>
